--- a/backend/data/mlb/My_Pitcher_Listing.xlsx
+++ b/backend/data/mlb/My_Pitcher_Listing.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Players" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -9971,10 +9971,10 @@
         <v>1562</v>
       </c>
       <c r="C10" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="D10" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="E10" t="s">
         <v>1623</v>
@@ -10019,7 +10019,7 @@
         <v>28</v>
       </c>
       <c r="T10" t="s">
-        <v>3020</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="11" spans="1:20">
